--- a/.cursor/flat/schema_azure_mssql_dbo.xlsx
+++ b/.cursor/flat/schema_azure_mssql_dbo.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SourceSystem" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="DataQualityFindings" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="customers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="employees" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="inventory" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="products" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="purchase_order_items" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="purchase_orders" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="sales_order_items" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="sales_orders" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="stores" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="suppliers" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="__rt_meta" sheetId="15" state="hidden" r:id="rId15"/>
-    <sheet name="__rt_payload" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SourceSystem" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DataQualityFindings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="customers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="employees" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_order_items" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_orders" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_order_items" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_orders" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stores" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="suppliers" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__rt_meta" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="__rt_payload" sheetId="16" state="hidden" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'DataQualityFindings'!$A$1:$Z$65</definedName>
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"metadata":{"generated_at":"2026-03-30T08:36:23.118377+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer, serving as the primary key for the customers table.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"customers\" table stores non-nullable given names of customers as nvarchar strings using the \"SQL_Latin1_General_CP1_CI_AS\" collation.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the customer's email address, allowing up to 450 Unicode characters, and can be null.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as a nullable Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a customer record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the timestamp of the most recent update to a customer record and is required (non-null).","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"employee_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the \"employees\" table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with an employee, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"employees\" table stores the given name of an employee as a non-null, case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Stores the unique email address of an employee as a non-null nvarchar value up to 450 characters.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role of an employee as a non-null, case-insensitive string.","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"hire_date\" column in the \"employees\" table stores the non-nullable date an employee was hired.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the employee record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to an employee record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"employees\" table stores information about employees, including their unique identifier, associated store, personal details, job role, hire date, and record timestamps.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a store, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product in the products table, establishing a foreign key relationship.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Represents the current quantity of a product in stock, stored as a non-null integer.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum stock quantity at which inventory should be reordered, stored as a non-null integer.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The \"last_restocked_at\" column records the timestamp of the most recent restocking event for an inventory item and allows null values.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `inventory` table stores the non-nullable timestamp indicating when a record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `inventory` table stores the non-nullable timestamp indicating the last update to a record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"co</t>
+          <t>{"metadata":{"generated_at":"2026-03-30T08:36:23.118377+00:00","database_url":"pioneertest.database.windows.net:1433/free-sql-db-3300567?driver=ODBC+Driver+18+for+SQL+Server&amp;TrustServerCertificate=yes","schema_filter":"dbo","total_tables":10,"total_rows":1364,"total_findings":64},"connection":{"host":"pioneertest.database.windows.net","port":"1433","database":"free-sql-db-3300567","driver":"mssql","timezone":"(UTC) Coordinated Universal Time"},"source_system_context":{"contacts":[],"delete_management_instruction":"","restrictions":"","late_arriving_data_manual":"","volume_size_projection_manual":"","system_description":"Azure SQL operational database (schema dbo) for a small retail operation: parties (customers, employees, suppliers), stores, products and inventory, and purchase/sales orders with line-level detail. Used for ingestion-readiness and data-quality analysis; sample data is synthetic-style test content.","db_analysis_config":{"exclude_schemas":["prediction"],"exclude_tables":[],"max_row_limit":100}},"concept_registry":{"version":1,"taxonomy":"domain-dot","generated_from_tables":10,"concepts":[{"concept_id":"contact.address","column_count":2,"table_count":1,"avg_confidence":0.55,"alias_groups":["address","postal_code"],"sample_columns":["stores.address","stores.postal_code"],"signals":["name","type"]},{"concept_id":"contact.email","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["email"],"sample_columns":["customers.email","employees.email","suppliers.email"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"contact.person_name","column_count":8,"table_count":5,"avg_confidence":0.56,"alias_groups":["contact_name","first_name","last_name","name"],"sample_columns":["customers.first_name","customers.last_name","employees.first_name","employees.last_name","products.name"],"signals":["name","table_context","type"]},{"concept_id":"contact.phone","column_count":3,"table_count":3,"avg_confidence":1.0,"alias_groups":["phone"],"sample_columns":["customers.phone","stores.phone","suppliers.phone"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"entity.category","column_count":1,"table_count":1,"avg_confidence":0.8,"alias_groups":["category"],"sample_columns":["products.category"],"signals":["name","profile","type"]},{"concept_id":"entity.status","column_count":2,"table_count":2,"avg_confidence":1.0,"alias_groups":["statu"],"sample_columns":["purchase_orders.status","sales_orders.status"],"signals":["name","profile","type","values"]},{"concept_id":"entity.type","column_count":1,"table_count":1,"avg_confidence":0.65,"alias_groups":["role"],"sample_columns":["employees.role"],"signals":["name","profile","type"]},{"concept_id":"finance.currency_amount","column_count":5,"table_count":4,"avg_confidence":1.0,"alias_groups":["amount","price","unit_cost"],"sample_columns":["products.unit_price","products.cost_price","purchase_order_items.unit_cost","sales_order_items.unit_price","sales_orders.total_amount"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"identifier.foreign_key","column_count":26,"table_count":10,"avg_confidence":0.78,"alias_groups":["id"],"sample_columns":["customers.customer_id","employees.employee_id","employees.store_id","inventory.inventory_id","inventory.store_id"],"signals":["cross_table_consensus","name","profile","type"]},{"concept_id":"identifier.product_code","column_count":1,"table_count":1,"avg_confidence":0.7,"alias_groups":["sku"],"sample_columns":["products.sku"],"signals":["name","profile","type"]},{"concept_id":"measure.quantity","column_count":7,"table_count":3,"avg_confidence":1.0,"alias_groups":["ordered_qty","ordered_qty_unit","quantity","quantity_on_hand","sold_qty","sold_qty_unit"],"sample_columns":["inventory.quantity_on_hand","purchase_order_items.quantity","purchase_order_items.ordered_qty_value","purchase_order_items.ordered_qty_unit","sales_order_items.quantity"],"signals":["name","profile","type","values"]},{"concept_id":"temporal.created_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["created_at"],"sample_columns":["customers.created_at","employees.created_at","inventory.created_at","products.created_at","purchase_order_items.created_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.date_only","column_count":4,"table_count":3,"avg_confidence":0.97,"alias_groups":["expected_date","hire_date","order_date"],"sample_columns":["employees.hire_date","purchase_orders.order_date","purchase_orders.expected_date","sales_orders.order_date"],"signals":["cross_table_consensus","name","profile","table_context","type","values"]},{"concept_id":"temporal.event_time","column_count":1,"table_count":1,"avg_confidence":1.0,"alias_groups":["last_restocked_at"],"sample_columns":["inventory.last_restocked_at"],"signals":["name","profile","table_context","type","values"]},{"concept_id":"temporal.updated_at","column_count":10,"table_count":10,"avg_confidence":1.0,"alias_groups":["updated_at"],"sample_columns":["customers.updated_at","employees.updated_at","inventory.updated_at","products.updated_at","purchase_order_items.updated_at"],"signals":["name","profile","table_context","type","values"]}]},"data_quality_summary":{"critical":0,"warning":27,"info":37,"by_check":{"controlled_value_candidate":7,"nullable_but_never_null":13,"missing_primary_key":0,"missing_foreign_key":0,"format_inconsistency":0,"range_violation":0,"timestamp_ordering":10,"delete_management":10,"late_arriving_data":3,"timezone":10,"unit_unknown":11,"unit_noncanonical_but_convertible":0,"unit_mismatch_within_semantic_group":0},"constraints_found":{"check_constraints":0,"enum_columns":0,"unique_constraints":10}},"tables":[{"table":"customers","schema":"dbo","columns":[{"name":"customer_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each customer, serving as the primary key for the customers table.","cardinality":100,"null_count":0,"data_range":{"min":"404","max":"503"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"customers\" table stores non-nullable given names of customers as nvarchar strings using the \"SQL_Latin1_General_CP1_CI_AS\" collation.","cardinality":100,"null_count":0,"data_range":{"min":"Customer1","max":"Customer99"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"customers\" table stores the non-nullable family name of a customer as a case-insensitive Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"LastName1 (updated)","max":"LastName99"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.6,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","table context: customers"],"concept_sources":["name","table_context","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":true,"is_incremental":false,"column_description":"Stores the customer's email address, allowing up to 450 Unicode characters, and can be null.","cardinality":100,"null_count":0,"data_range":{"min":"customer1@example.com","max":"customer99@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the customer's phone number as a nullable Unicode string.","cardinality":100,"null_count":0,"data_range":{"min":"555-1001","max":"555-1100"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","table context: customers","sensitive hint: pii_contact"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a customer record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-02-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the timestamp of the most recent update to a customer record and is required (non-null).","column_timezone":"(UTC) Coordinated Universal Time","cardinality":95,"null_count":0,"data_range":{"min":"2021-03-23 15:38:57.201565","max":"2026-03-26 08:52:49.252228"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: customers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"customers\" table stores information about customers, including their unique ID, name, contact details, and timestamps for record creation and updates.","primary_keys":["customer_id"],"foreign_keys":[],"row_count":100,"field_classifications":{"customer_id":"identifier","first_name":"person_name","last_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":126,"row_count_projection_2y":152,"row_count_projection_5y":232,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"employees","schema":"dbo","columns":[{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"employee_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying employees in the \"employees\" table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with an employee, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"first_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"first_name\" column in the \"employees\" table stores the given name of an employee as a non-null, case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"Employee1","max":"Employee9"},"data_category":"nominal","semantic_class":"given_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: first_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"first_name"},{"name":"last_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"last_name\" column in the \"employees\" table stores the non-nullable family name of an employee as a case-insensitive Unicode string.","cardinality":20,"null_count":0,"data_range":{"min":"LastName1","max":"LastName9"},"data_category":"nominal","semantic_class":"family_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: last_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"last_name"},{"name":"email","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"Stores the unique email address of an employee as a non-null nvarchar value up to 450 characters.","cardinality":20,"null_count":0,"data_range":{"min":"emp1@example.com","max":"emp9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar(450)","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"role","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the job role of an employee as a non-null, case-insensitive string.","cardinality":4,"null_count":0,"data_range":{"min":"Cashier","max":"Stock"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"entity.type","concept_confidence":0.65,"concept_evidence":["name token: role","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"role"},{"name":"hire_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"hire_date\" column in the \"employees\" table stores the non-nullable date an employee was hired.","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03","max":"2025-01-26"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: hire_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"hire_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the employee record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to an employee record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":20,"null_count":0,"data_range":{"min":"2021-05-03 15:38:57.201565","max":"2025-01-26 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: employees"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"employees\" table stores information about employees, including their unique identifier, associated store, personal details, job role, hire date, and record timestamps.","primary_keys":["employee_id"],"foreign_keys":[{"column":"store_id","references":"stores.store_id"}],"row_count":20,"field_classifications":{"first_name":"person_name","last_name":"person_name","email":"contact","hire_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":true,"row_count_projection_1y":35,"row_count_projection_2y":50,"row_count_projection_5y":96,"partition_columns_candidates":["hire_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"entity.type":1,"identifier.foreign_key":2,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":["first_name","last_name"]},"data_quality":{"findings":[{"column":"role","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 4 distinct value(s) ('Cashier', 'Manager', 'Sales', 'Stock') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cashier","Manager","Sales","Stock"],"cardinality":4},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"hire_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'hire_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'hire_date', add a 1\u20132 day lookback buffer.","business_date_column":"hire_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":20,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"inventory","schema":"dbo","columns":[{"name":"inventory_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `inventory_id` column is a non-nullable bigint serving as the primary key for uniquely identifying records in the `inventory` table.","cardinality":100,"null_count":0,"data_range":{"min":"8","max":"107"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a store, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of a product in the products table, establishing a foreign key relationship.","cardinality":47,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity_on_hand","type":"integer","nullable":false,"is_incremental":false,"column_description":"Represents the current quantity of a product in stock, stored as a non-null integer.","cardinality":68,"null_count":0,"data_range":{"min":"2","max":"98"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity_on_hand","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity_on_hand"},{"name":"reorder_level","type":"integer","nullable":false,"is_incremental":false,"column_description":"Indicates the minimum stock quantity at which inventory should be reordered, stored as a non-null integer.","cardinality":20,"null_count":0,"data_range":{"min":"10","max":"29"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: integer","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"last_restocked_at","type":"datetime2","nullable":true,"is_incremental":false,"column_description":"The \"last_restocked_at\" column records the timestamp of the most recent restocking event for an inventory item and allows null values.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.event_time","concept_confidence":1.0,"concept_evidence":["name token: last_restocked_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"last_restocked_at"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The `created_at` column in the `inventory` table stores the non-nullable timestamp indicating when a record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":91,"null_count":0,"data_range":{"min":"2024-03-05 15:38:57.201565","max":"2026-02-23 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The `updated_at` column in the `inventory` table stores the non-nullable timestamp indicating the last update to a record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":89,"null_count":0,"data_range":{"min":"2024-03-14 15:38:57.201565","max":"2026-03-07 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: inventory"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"stock_value","type":"numeric(10,2)","nullable":true,"is_incremental":fal</t>
         </is>
       </c>
     </row>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ncept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `product_id` column is a non-nullable bigint serving as the primary key for uniquely identifying products in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the supplier associated with a product, referencing the `supplier_id` column in the `suppliers` table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"sku\" column stores a unique alphanumeric identifier for products, with a maximum length of 450 characters, and cannot be null.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the product as a non-null Unicode string.","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the category of the product, stored as a non-null case-insensitive Unicode string.","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Stores the price per unit of a product as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null numeric cost price of a product, stored with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether the product is active (True) or inactive (False).","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Indicates the timestamp when the product record was created, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a product record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the weight of the product as a numeric value with up to 10 digits and 2 decimal places, nullable.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the length measurement of a product as a numeric value with up to 10 digits and 2 decimal places, which can be null.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores an optional textual description of the product.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item, serving as the primary key for the table.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated purchase order in the purchase_orders table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the associated product in the purchase order item, referencing the `products.product_id` column.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table stores a non-null integer representing the number of items in a purchase order.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a purchase order item, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to the purchase_order_items entry, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the ordered quantity for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_id` column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `purchase_orders` table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier</t>
+          <t>se,"column_description":"Represents the monetary value of stock for an inventory item, stored as a numeric value with up to 10 digits and 2 decimal places, and may be null.","cardinality":0,"null_count":100,"data_category":"continuous","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"stock_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Current stock unit label.","cardinality":0,"null_count":100,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null}],"table_description":"Current stock levels with normalized stock unit representation.","primary_keys":["inventory_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":100,"field_classifications":{"quantity_on_hand":"quantity","last_restocked_at":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":["quantity_on_hand"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":146,"row_count_projection_2y":193,"row_count_projection_5y":334,"partition_columns_candidates":["last_restocked_at","created_at","updated_at"],"classification_summary":{"concept_counts":{"identifier.foreign_key":3,"measure.quantity":1,"temporal.created_at":1,"temporal.event_time":1,"temporal.updated_at":1},"low_confidence_columns":["reorder_level","stock_unit"]},"data_quality":{"findings":[{"column":"last_restocked_at","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 100 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"last_restocked_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3},{"column":"quantity_on_hand","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"products","schema":"dbo","columns":[{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `product_id` column is a non-nullable bigint serving as the primary key for uniquely identifying products in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the supplier associated with a product, referencing the `supplier_id` column in the `suppliers` table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"sku","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"The \"sku\" column stores a unique alphanumeric identifier for products, with a maximum length of 450 characters, and cannot be null.","cardinality":50,"null_count":0,"data_range":{"min":"SKU-0001","max":"SKU-0050"},"data_category":"nominal","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.product_code","concept_confidence":0.7,"concept_evidence":["name token: sku","type hint: nvarchar(450)","semantic class hint: product_identifier"],"concept_sources":["name","profile","type"],"concept_alias_group":"sku"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the product as a non-null Unicode string.","cardinality":50,"null_count":0,"data_range":{"min":"Product 1","max":"Product 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"category","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the category of the product, stored as a non-null case-insensitive Unicode string.","cardinality":5,"null_count":0,"data_range":{"min":"Books","max":"Sports"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.category","concept_confidence":0.8,"concept_evidence":["name token: category","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","profile heuristic matched"],"concept_sources":["name","profile","type"],"concept_alias_group":"category"},{"name":"unit_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Stores the price per unit of a product as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"cost_price","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the non-null numeric cost price of a product, stored with up to 10 digits and 2 decimal places.","cardinality":50,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"price"},{"name":"active","type":"bit","nullable":false,"is_incremental":false,"column_description":"Indicates whether the product is active (True) or inactive (False).","cardinality":1,"null_count":0,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.0,"concept_evidence":["profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile"],"concept_alias_group":null},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Indicates the timestamp when the product record was created, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a product record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":50,"null_count":0,"data_range":{"min":"2021-03-20 15:38:57.201565","max":"2024-12-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: products"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"weight_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source weight unit (kg/lb) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"weight_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the weight of the product as a numeric value with up to 10 digits and 2 decimal places, nullable.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"mass","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Stores the length measurement of a product as a numeric value with up to 10 digits and 2 decimal places, which can be null.","cardinality":0,"null_count":50,"data_category":"continuous","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.0,"concept_evidence":["type hint: numeric(10,2)","ambiguous runner-up concept"],"concept_sources":["type"],"concept_alias_group":null},{"name":"length_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Source length unit (cm/in) used for unit inference testing.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":"length","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":null,"concept_confidence":0.15,"concept_evidence":["value pattern: quantity","ambiguous runner-up concept"],"concept_sources":["values"],"concept_alias_group":null},{"name":"product_description","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores an optional textual description of the product.","cardinality":0,"null_count":50,"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"primary_supplier_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Primary supplier relationship used for join candidate detection.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Master product catalog including physical units for analyzer unit-context testing.","primary_keys":["product_id"],"foreign_keys":[{"column":"primary_supplier_id","references":"suppliers.supplier_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":50,"field_classifications":{"category":"categorical","unit_price":"pricing","cost_price":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"primary_supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":16,"mixed_unit_groups":[],"unknown_unit_columns":["length_unit","length_value","weight_unit","weight_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":68,"row_count_projection_2y":86,"row_count_projection_5y":141,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.person_name":1,"entity.category":1,"finance.currency_amount":2,"identifier.foreign_key":3,"identifier.product_code":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["length_unit","name","product_description","weight_unit"]},"data_quality":{"findings":[{"column":"category","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('Books', 'Clothing', 'Electronics', 'Home', 'Sports') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Books","Clothing","Electronics","Home","Sports"],"cardinality":5},{"column":"primary_supplier_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 50 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":"active","check":"delete_management","severity":"info","detail":"Active-flag column 'active' (boolean) detected \u2014 rows with active=false are logically deleted. Current distribution: True=50.","recommendation":"Filter on \"active\" = true for current records during ingestion.","delete_strategy":"soft_delete","soft_delete_column":"active","soft_delete_type":"active_flag","has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"weight_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"weight_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'mass' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"length_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'length' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_order_items","schema":"dbo","columns":[{"name":"po_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each purchase order item, serving as the primary key for the table.","cardinality":246,"null_count":0,"data_range":{"min":"268","max":"513"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated purchase order in the purchase_orders table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Identifies the associated product in the purchase order item, referencing the `products.product_id` column.","cardinality":49,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"purchase_order_items\" table stores a non-null integer representing the number of items in a purchase order.","cardinality":41,"null_count":0,"data_range":{"min":"10","max":"50"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_cost","type":"numeric(10,2)","nullable":false,"is_incremental":false,"column_description":"Represents the per-unit cost of a purchase order item, stored as a non-null numeric value with up to 10 digits and 2 decimal places.","cardinality":49,"null_count":0,"data_range":{"min":"5.55","max":"358.59"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: unit_cost","type hint: numeric(10,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"unit_cost"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order item record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668789","max":"2026-03-12 15:45:45.174099"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Records the timestamp of the most recent update to the purchase_order_items entry, stored as a non-nullable datetime2 value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":246,"null_count":0,"data_range":{"min":"2026-03-12 15:44:18.668794","max":"2026-03-12 15:45:45.174104"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"ordered_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the ordered quantity for a purchase order item, allowing up to 10 digits with 2 decimal places, and can be null.","cardinality":0,"null_count":246,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"ordered_qty"},{"name":"ordered_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Ordered quantity unit (ea/box).","cardinality":0,"null_count":246,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: ordered_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"ordered_qty_unit"}],"table_description":"Line items with order quantities and explicit unit labels.","primary_keys":["po_item_id"],"foreign_keys":[{"column":"po_id","references":"purchase_orders.po_id"},{"column":"product_id","references":"products.product_id"}],"row_count":246,"field_classifications":{"quantity":"quantity","unit_cost":"pricing","created_at":"temporal","updated_at":"temporal","ordered_qty_value":"quantity","ordered_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"po_id","target_table":"purchase_orders","target_column":"po_id","confidence":"high"},{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["ordered_qty_unit","ordered_qty_value","quantity"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":246,"row_count_projection_2y":246,"row_count_projection_5y":246,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"ordered_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"purchase_orders","schema":"dbo","columns":[{"name":"po_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The `po_id`</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10215,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the supplier associated with the purchase order, linking to the `suppliers.supplier_id` column.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of the purchase order, such as 'Ordered' or 'Received', stored as a non-nullable nvarchar value.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column in the \"purchase_orders\" table stores the non-nullable date when the purchase order was placed.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The \"expected_date\" column in the \"purchase_orders\" table stores the anticipated delivery date of a purchase order and allows null values.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a purchase order record, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order item, serving as the primary key in the sales_order_items table.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated sales order in the sales_orders table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a product associated with a sales order item, referencing the `product_id` column in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores a non-null integer representing the number of items in a sales order.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The \"unit_price\" column stores the non-null numeric price per unit of a sales order item, with up to 15 digits and 2 decimal places, in a currency amount format.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order item was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a sales order item record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the sold quantity for a sales order item, allowing nulls.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"The \"customer_id\" column in the \"sales_orders\" table is a nullable bigint that references the \"customer_id\" column in the \"customers\" table, identifying the customer associated with a sales order.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the employees table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column stores the date and time when a sales order was placed, using the datetime2 data type, and cannot be null.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed'.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"Represents the total monetary amount for a sales order, stored as a non-null numeric value with up to 12 digits and 2 decimal places.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order entry was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to a sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"wa</t>
+          <t xml:space="preserve"> column is a non-nullable bigint serving as the primary key for uniquely identifying purchase orders in the `purchase_orders` table.","cardinality":125,"null_count":0,"data_range":{"min":"128","max":"252"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the supplier associated with the purchase order, linking to the `suppliers.supplier_id` column.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the identifier of the store associated with the purchase order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of the purchase order, such as 'Ordered' or 'Received', stored as a non-nullable nvarchar value.","cardinality":3,"null_count":0,"data_range":{"min":"Ordered","max":"Received"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"order_date","type":"date","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column in the \"purchase_orders\" table stores the non-nullable date when the purchase order was placed.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09","max":"2026-03-12"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: order_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"order_date"},{"name":"expected_date","type":"date","nullable":true,"is_incremental":false,"column_description":"The \"expected_date\" column in the \"purchase_orders\" table stores the anticipated delivery date of a purchase order and allows null values.","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-27","max":"2026-03-31"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":1.0,"concept_evidence":["name token: expected_date","type hint: date","legacy field classification: temporal","value pattern: date_only","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"expected_date"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when the purchase order record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"Tracks the timestamp of the most recent update to a purchase order record, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":123,"null_count":0,"data_range":{"min":"2021-04-09 15:38:57.201565","max":"2026-03-12 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: purchase_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"approver_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Approver employee foreign key for procurement workflow.","cardinality":0,"null_count":125,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Procurement headers including approver employee relationship.","primary_keys":["po_id"],"foreign_keys":[{"column":"approver_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"},{"column":"supplier_id","references":"suppliers.supplier_id"}],"row_count":125,"field_classifications":{"status":"categorical","order_date":"temporal","expected_date":"temporal","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"approver_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"},{"column":"supplier_id","target_table":"suppliers","target_column":"supplier_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":155,"row_count_projection_2y":185,"row_count_projection_5y":276,"partition_columns_candidates":["order_date","expected_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"identifier.foreign_key":4,"temporal.created_at":1,"temporal.date_only":2,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Ordered', 'Pending', 'Received') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Ordered","Pending","Received"],"cardinality":3},{"column":"expected_date","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 125 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Minor arrival delay \u2014 max lag between 'order_date' and 'created_at' is 15.7h (avg 15.7h, P95 15.7h).","recommendation":"Use 'created_at' as the watermark (preferred). If using 'order_date', add a 1\u20132 day lookback buffer.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":125,"min_lag_hours":15.65,"avg_lag_hours":15.65,"p95_lag_hours":15.65,"max_lag_hours":15.65,"max_lag_days":0.7,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":2},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"sales_order_items","schema":"dbo","columns":[{"name":"sales_order_item_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order item, serving as the primary key in the sales_order_items table.","cardinality":508,"null_count":0,"data_range":{"min":"497","max":"1004"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"References the unique identifier of the associated sales order in the sales_orders table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"product_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of a product associated with a sales order item, referencing the `product_id` column in the `products` table.","cardinality":50,"null_count":0,"data_range":{"min":"156","max":"205"},"data_category":"discrete","semantic_class":"product_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"quantity","type":"integer","nullable":false,"is_incremental":false,"column_description":"The \"quantity\" column in the \"sales_order_items\" table stores a non-null integer representing the number of items in a sales order.","cardinality":5,"null_count":0,"data_range":{"min":"1","max":"5"},"data_category":"discrete","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: quantity","type hint: integer","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"quantity"},{"name":"unit_price","type":"numeric(15,2)","nullable":false,"is_incremental":false,"column_description":"The \"unit_price\" column stores the non-null numeric price per unit of a sales order item, with up to 15 digits and 2 decimal places, in a currency amount format.","cardinality":50,"null_count":0,"data_range":{"min":"11.09","max":"490.43"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: price","type hint: numeric(15,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"price"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order item was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155388","max":"2026-03-12 15:43:38.264437"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update made to a sales order item record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":508,"null_count":0,"data_range":{"min":"2026-03-12 15:41:01.155390","max":"2026-03-12 15:43:38.264447"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_order_items"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sold_qty_value","type":"numeric(10,2)","nullable":true,"is_incremental":false,"column_description":"Represents the numeric value of the sold quantity for a sales order item, allowing nulls.","cardinality":0,"null_count":508,"data_category":"continuous","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty","type hint: numeric(10,2)","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"sold_qty"},{"name":"sold_qty_unit","type":"nvarchar(16)","nullable":true,"is_incremental":false,"column_description":"Sold quantity unit (ea/box).","cardinality":0,"null_count":508,"data_category":"nominal","semantic_class":"quantity","unit_context":{"detected_unit":null,"canonical_unit":null,"unit_system":"unknown","conversion":null,"detection_confidence":"low","detection_source":"combined","notes":"Semantic class suggests units, but no explicit source unit token was detected."},"concept_id":"measure.quantity","concept_confidence":1.0,"concept_evidence":["name token: sold_qty_unit","legacy field classification: quantity","semantic class hint: quantity","value pattern: quantity"],"concept_sources":["name","profile","values"],"concept_alias_group":"sold_qty_unit"}],"table_description":"Sales line items with sold quantity and explicit unit labels.","primary_keys":["sales_order_item_id"],"foreign_keys":[{"column":"product_id","references":"products.product_id"},{"column":"sales_order_id","references":"sales_orders.sales_order_id"}],"row_count":508,"field_classifications":{"quantity":"quantity","unit_price":"pricing","created_at":"temporal","updated_at":"temporal","sold_qty_value":"quantity","sold_qty_unit":"quantity"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"product_id","target_table":"products","target_column":"product_id","confidence":"high"},{"column":"sales_order_id","target_table":"sales_orders","target_column":"sales_order_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":9,"mixed_unit_groups":[],"unknown_unit_columns":["quantity","sold_qty_unit","sold_qty_value"]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":508,"row_count_projection_2y":508,"row_count_projection_5y":508,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"finance.currency_amount":1,"identifier.foreign_key":3,"measure.quantity":3,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2},{"column":"quantity","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_value","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."},{"column":"sold_qty_unit","check":"unit_unknown","severity":"warning","detail":"Column semantic class 'quantity' has unknown source units.","recommendation":"Add explicit source unit mapping for this field to enable safe aggregation."}]}},{"table":"sales_orders","schema":"dbo","columns":[{"name":"sales_order_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each sales order in the table.","cardinality":200,"null_count":0,"data_range":{"min":"375","max":"574"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the store associated with the sales order, referencing the `store_id` column in the `stores` table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"customer_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"The \"customer_id\" column in the \"sales_orders\" table is a nullable bigint that references the \"customer_id\" column in the \"customers\" table, identifying the customer associated with a sales order.","cardinality":76,"null_count":0,"data_range":{"min":"404","max":"502"},"data_category":"discrete","semantic_class":"customer_identifier","unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"employee_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Represents the unique identifier of the employee associated with the sales order, referencing the employees table.","cardinality":20,"null_count":0,"data_range":{"min":"64","max":"83"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"},{"name":"order_date","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"order_date\" column stores the date and time when a sales order was placed, using the datetime2 data type, and cannot be null.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.date_only","concept_confidence":0.9,"concept_evidence":["name token: order_date","type hint: datetime2","legacy field classification: temporal","table context: sales_orders","cross-table consensus: 2 similar columns"],"concept_sources":["cross_table_consensus","name","profile","table_context","type"],"concept_alias_group":"order_date"},{"name":"status","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Indicates the current state of a sales order, such as 'Pending' or 'Completed'.","cardinality":3,"null_count":0,"data_range":{"min":"Completed","max":"Shipped"},"data_category":"nominal","semantic_class":"category","unit_context":null,"concept_id":"entity.status","concept_confidence":1.0,"concept_evidence":["name token: statu","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: categorical","value pattern: status","profile heuristic matched"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"statu"},{"name":"total_amount","type":"numeric(12,2)","nullable":false,"is_incremental":false,"column_description":"Represents the total monetary amount for a sales order, stored as a non-null numeric value with up to 12 digits and 2 decimal places.","cardinality":200,"null_count":0,"data_range":{"min":"66.47","max":"998.76"},"data_category":"continuous","semantic_class":"currency_amount","unit_context":null,"concept_id":"finance.currency_amount","concept_confidence":1.0,"concept_evidence":["name token: amount","type hint: numeric(12,2)","legacy field classification: pricing","semantic class hint: currency_amount","value pattern: currency_amount","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"amount"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"Records the timestamp when the sales order entry was created, stored as a non-nullable datetime value.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the most recent update to a sales order record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":191,"null_count":0,"data_range":{"min":"2021-03-14 15:38:57.201565","max":"2026-03-11 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: sales_orders"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"},{"name":"sales_rep_employee_id","type":"bigint","nullable":true,"is_incremental":false,"column_description":"Sales representative foreign key for order ownership.","cardinality":0,"null_count":200,"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.9,"concept_evidence":["name token: id","type hint: bigint","structural hint: join candidate"],"concept_sources":["name","profile","type"],"concept_alias_group":"id"}],"table_description":"Sales headers including assigned sales representative relationship.","primary_keys":["sales_order_id"],"foreign_keys":[{"column":"customer_id","references":"customers.customer_id"},{"column":"employee_id","references":"employees.employee_id"},{"column":"sales_rep_employee_id","references":"employees.employee_id"},{"column":"store_id","references":"stores.store_id"}],"row_count":200,"field_classifications":{"customer_id":"identifier","order_date":"temporal","status":"categorical","total_amount":"pricing","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{},"incremental_columns":["updated_at"],"join_candidates":[{"column":"customer_id","target_table":"customers","target_column":"customer_id","confidence":"high"},{"column":"employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"sales_rep_employee_id","target_table":"employees","target_column":"employee_id","confidence":"high"},{"column":"store_id","target_table":"stores","target_column":"store_id","confidence":"high"}],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":true,"has_sensitive_fields":false,"row_count_projection_1y":242,"row_count_projection_2y":284,"row_count_projection_5y":412,"partition_columns_candidates":["order_date","created_at","updated_at"],"classification_summary":{"concept_counts":{"entity.status":1,"finance.currency_amount":1,"identifier.foreign_key":5,"temporal.created_at":1,"temporal.date_only":1,"temporal.updated_at":1},"low_confidence_columns":[]},"data_quality":{"findings":[{"column":"status","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Completed', 'Pending', 'Shipped') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Completed","Pending","Shipped"],"cardinality":3},{"column":"customer_id","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 200 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'c</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10225,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"store_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the \"stores\" table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field intended to store the name of a store.","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"A non-nullable nvarchar(450) column storing unique alphanumeric identifiers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the address of a store as a nullable nvarchar string.","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.city is a nullable nvarchar column storing the name of the city where a store is located.","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"This column stores the state or province associated with a store, allowing null values.","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores optional alphanumeric postal codes for store locations.","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing contact phone numbers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a store record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp indicating the last update time of a store record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table contains information about individual store locations, including identifiers, contact details, and timestamps for record creation and updates.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the non-nullable primary key of the table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the supplier as a non-null Unicode string.","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the contact person for a supplier, allowing null values.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the supplier's email address as a nullable nvarchar value with case-insensitive collation.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the supplier's phone number as a nullable text field.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update to a supplier record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
+          <t>reated_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":"order_date","check":"late_arriving_data","severity":"info","detail":"Data arrives promptly \u2014 max lag between 'order_date' and 'created_at' is 0.0h. Standard watermarking on 'created_at' is safe.","recommendation":"Use 'created_at' as the incremental watermark. No special lookback window needed.","business_date_column":"order_date","system_ts_column":"created_at","lag_stats":{"total_rows_compared":200,"min_lag_hours":0.0,"avg_lag_hours":0.0,"p95_lag_hours":0.0,"max_lag_hours":0.0,"max_lag_days":0.0,"rows_late_over_1d":0,"rows_late_over_7d":0},"recommended_lookback_days":1},{"column":null,"check":"timezone","severity":"info","detail":"All 3 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"order_date","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":3}]}},{"table":"stores","schema":"dbo","columns":[{"name":"store_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"The \"store_id\" column is a non-nullable bigint serving as the primary key for uniquely identifying each store in the \"stores\" table.","cardinality":5,"null_count":0,"data_range":{"min":"19","max":"23"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"The \"name\" column in the \"stores\" table is a non-nullable nvarchar field intended to store the name of a store.","cardinality":5,"null_count":0,"data_range":{"min":"Airport Shop","max":"Suburb Store"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"code","type":"nvarchar(450)","nullable":false,"is_incremental":false,"column_description":"A non-nullable nvarchar(450) column storing unique alphanumeric identifiers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"AIR","max":"SUB"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar(450)","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"address","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"address\" column in the \"stores\" table stores the address of a store as a nullable nvarchar string.","cardinality":5,"null_count":0,"data_range":{"min":"1 Main St","max":"5 Main St"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: address","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"address"},{"name":"city","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.city is a nullable nvarchar column storing the name of the city where a store is located.","cardinality":3,"null_count":0,"data_range":{"min":"Cork","max":"Limerick"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"state","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"This column stores the state or province associated with a store, allowing null values.","cardinality":3,"null_count":0,"data_range":{"min":"Connacht","max":"Munster"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":null,"concept_confidence":0.1,"concept_evidence":["type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","profile heuristic matched","ambiguous runner-up concept"],"concept_sources":["profile","type"],"concept_alias_group":null},{"name":"postal_code","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"postal_code\" column in the \"stores\" table stores optional alphanumeric postal codes for store locations.","cardinality":5,"null_count":0,"data_range":{"min":"10000","max":"10004"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.address","concept_confidence":0.55,"concept_evidence":["name token: postal_code","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"postal_code"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores.phone is an optional nvarchar column storing contact phone numbers for stores.","cardinality":5,"null_count":0,"data_range":{"min":"555-3000","max":"555-3004"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a store record was initially created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp indicating the last update time of a store record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":5,"null_count":0,"data_range":{"min":"2021-07-26 15:38:57.201565","max":"2025-01-31 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: stores"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"stores\" table contains information about individual store locations, including identifiers, contact details, and timestamps for record creation and updates.","primary_keys":["store_id"],"foreign_keys":[],"row_count":5,"field_classifications":{"phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"address":"pii_address","postal_code":"pii_address","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":10,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":17,"row_count_projection_2y":29,"row_count_projection_5y":65,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.address":2,"contact.person_name":1,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["address","city","code","name","postal_code","state"]},"data_quality":{"findings":[{"column":"city","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Cork', 'Galway', 'Limerick') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Cork","Galway","Limerick"],"cardinality":3},{"column":"state","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 3 distinct value(s) ('Connacht', 'Leinster', 'Munster') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["Connacht","Leinster","Munster"],"cardinality":3},{"column":"postal_code","check":"controlled_value_candidate","severity":"warning","detail":"Text column with 5 distinct value(s) ('10000', '10001', '10002', '10003', '10004') but no CHECK, ENUM, or FK constraint","recommendation":"Add a CHECK constraint, convert to an ENUM type, or create a lookup/reference table to prevent invalid values","distinct_values":["10000","10001","10002","10003","10004"],"cardinality":5},{"column":"address","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"city","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"state","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"postal_code","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 5 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}},{"table":"suppliers","schema":"dbo","columns":[{"name":"supplier_id","type":"bigint","nullable":false,"is_incremental":false,"column_description":"Unique identifier for each supplier, serving as the non-nullable primary key of the table.","cardinality":10,"null_count":0,"data_range":{"min":"33","max":"42"},"data_category":"discrete","semantic_class":null,"unit_context":null,"concept_id":"identifier.foreign_key","concept_confidence":0.6,"concept_evidence":["name token: id","type hint: bigint","cross-table consensus: 16 similar columns","ambiguous runner-up concept"],"concept_sources":["cross_table_consensus","name","type"],"concept_alias_group":"id"},{"name":"name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":false,"is_incremental":false,"column_description":"Stores the name of the supplier as a non-null Unicode string.","cardinality":10,"null_count":0,"data_range":{"min":"Supplier 1","max":"Supplier 9"},"data_category":"nominal","semantic_class":null,"unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"name"},{"name":"contact_name","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the name of the contact person for a supplier, allowing null values.","cardinality":0,"null_count":10,"data_category":"nominal","semantic_class":"person_name","unit_context":null,"concept_id":"contact.person_name","concept_confidence":0.55,"concept_evidence":["name token: contact_name","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\""],"concept_sources":["name","type"],"concept_alias_group":"contact_name"},{"name":"email","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"The \"email\" column in the \"suppliers\" table stores the supplier's email address as a nullable nvarchar value with case-insensitive collation.","cardinality":10,"null_count":0,"data_range":{"min":"supplier1@example.com","max":"supplier9@example.com"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.email","concept_confidence":1.0,"concept_evidence":["name token: email","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: email","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"email"},{"name":"phone","type":"nvarchar collate \"sql_latin1_general_cp1_ci_as\"","nullable":true,"is_incremental":false,"column_description":"Stores the supplier's phone number as a nullable text field.","cardinality":10,"null_count":0,"data_range":{"min":"555-2001","max":"555-2010"},"data_category":"nominal","semantic_class":"contact","unit_context":null,"concept_id":"contact.phone","concept_confidence":1.0,"concept_evidence":["name token: phone","type hint: nvarchar collate \"sql_latin1_general_cp1_ci_as\"","legacy field classification: contact","value pattern: phone","sensitive hint: pii_contact"],"concept_sources":["name","profile","type","values"],"concept_alias_group":"phone"},{"name":"created_at","type":"datetime2","nullable":false,"is_incremental":false,"column_description":"The \"created_at\" column stores the non-nullable timestamp indicating when a supplier record was created.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.created_at","concept_confidence":1.0,"concept_evidence":["name token: created_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"created_at"},{"name":"updated_at","type":"datetime2","nullable":false,"is_incremental":true,"column_description":"The \"updated_at\" column stores the non-nullable timestamp of the last update to a supplier record.","column_timezone":"(UTC) Coordinated Universal Time","cardinality":10,"null_count":0,"data_range":{"min":"2021-03-22 15:38:57.201565","max":"2024-02-25 15:38:57.201565"},"data_category":"continuous","semantic_class":"timestamp","unit_context":null,"concept_id":"temporal.updated_at","concept_confidence":1.0,"concept_evidence":["name token: updated_at","type hint: datetime2","legacy field classification: temporal","value pattern: timestamp","table context: suppliers"],"concept_sources":["name","profile","table_context","type","values"],"concept_alias_group":"updated_at"}],"table_description":"The \"suppliers\" table stores information about suppliers, including their unique identifier, name, contact details, and timestamps for record creation and updates.","primary_keys":["supplier_id"],"foreign_keys":[],"row_count":10,"field_classifications":{"contact_name":"person_name","email":"contact","phone":"contact","created_at":"temporal","updated_at":"temporal"},"sensitive_fields":{"email":"pii_contact","phone":"pii_contact"},"incremental_columns":["updated_at"],"join_candidates":[],"unit_summary":{"columns_with_units":0,"columns_without_units":7,"mixed_unit_groups":[],"unknown_unit_columns":[]},"cdc_enabled":false,"has_primary_key":true,"has_foreign_keys":false,"has_sensitive_fields":true,"row_count_projection_1y":22,"row_count_projection_2y":35,"row_count_projection_5y":74,"partition_columns_candidates":["created_at","updated_at"],"classification_summary":{"concept_counts":{"contact.email":1,"contact.person_name":2,"contact.phone":1,"identifier.foreign_key":1,"temporal.created_at":1,"temporal.updated_at":1},"low_confidence_columns":["contact_name","name"]},"data_quality":{"findings":[{"column":"email","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":"phone","check":"nullable_but_never_null","severity":"info","detail":"Column is nullable but has 0 NULLs across 10 row(s)","recommendation":"Consider adding a NOT NULL constraint if the column should always have a value"},{"column":null,"check":"timestamp_ordering","severity":"info","detail":"Table has both 'created_at' and 'updated_at' but no CHECK constraint guaranteeing created_at &lt;= updated_at.","recommendation":"Add CHECK (created_at &lt;= updated_at) to enforce temporal consistency.","created_column":"created_at","updated_column":"updated_at"},{"column":null,"check":"delete_management","severity":"warning","detail":"No soft-delete column detected and CDC is not enabled. Table likely uses hard deletes invisible to incremental ingestion.","recommendation":"Consider: (1) Add soft-delete column, (2) Enable CDC via ALTER TABLE \u2026 REPLICA IDENTITY FULL, or (3) Plan periodic full-load syncs.","delete_strategy":"hard_delete","soft_delete_column":null,"soft_delete_type":null,"has_audit_trail":false},{"column":null,"check":"timezone","severity":"info","detail":"All 2 date/time column(s) are TZ-naive \u2014 stored values are implicitly in server timezone '(UTC) Coordinated Universal Time'.","recommendation":"During ingestion, treat all timestamps as '(UTC) Coordinated Universal Time' and convert to UTC.","server_timezone":"(UTC) Coordinated Universal Time","columns":[{"column":"created_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false},{"column":"updated_at","type":"datetime2","effective_timezone":"(UTC) Coordinated Universal Time","is_tz_aware":false}],"distinct_timezones":["(UTC) Coordinated Universal Time"],"tz_aware_count":0,"tz_naive_count":2}]}}]}</t>
         </is>
       </c>
     </row>
